--- a/cds_files/IowaState_CDS_2022-2023.xlsx
+++ b/cds_files/IowaState_CDS_2022-2023.xlsx
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
